--- a/contact_forms/026_web_development_inquiry--contact_forms.xlsx
+++ b/contact_forms/026_web_development_inquiry--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Design'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'development'}</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Development'}</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'consulting'}</t>
+          <t>consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Consulting'}</t>
+          <t>Consulting</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_maintenance'}</t>
+          <t>in_maintenance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Maintenance'}</t>
+          <t>In Maintenance</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Website'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mobile_app'}</t>
+          <t>mobile_app</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mobile App'}</t>
+          <t>Mobile App</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'e-commerce'}</t>
+          <t>e-commerce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'E-commerce'}</t>
+          <t>E-commerce</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'landing_page'}</t>
+          <t>landing_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Landing Page'}</t>
+          <t>Landing Page</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'blog'}</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Blog'}</t>
+          <t>Blog</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'asia'}</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Asia'}</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'africa'}</t>
+          <t>africa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Africa'}</t>
+          <t>Africa</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'south_america'}</t>
+          <t>south_america</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'South America'}</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'free'}</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Free'}</t>
+          <t>Free</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'hourly'}</t>
+          <t>hourly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Hourly'}</t>
+          <t>Hourly</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'project'}</t>
+          <t>project</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Project'}</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'package'}</t>
+          <t>package</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Package'}</t>
+          <t>Package</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'partially_paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Partially Paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
